--- a/artfynd/A 36241-2023 artfynd.xlsx
+++ b/artfynd/A 36241-2023 artfynd.xlsx
@@ -895,11 +895,11 @@
         <v>116387200</v>
       </c>
       <c r="B4" t="n">
-        <v>56490</v>
+        <v>56593</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">

--- a/artfynd/A 36241-2023 artfynd.xlsx
+++ b/artfynd/A 36241-2023 artfynd.xlsx
@@ -895,11 +895,11 @@
         <v>116387200</v>
       </c>
       <c r="B4" t="n">
-        <v>56593</v>
+        <v>56490</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">

--- a/artfynd/A 36241-2023 artfynd.xlsx
+++ b/artfynd/A 36241-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,43 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115750658</v>
+        <v>115750616</v>
       </c>
       <c r="B2" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>856450</v>
+        <v>856542</v>
       </c>
       <c r="R2" t="n">
-        <v>7476261</v>
+        <v>7476203</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -757,17 +751,13 @@
           <t>2024-04-06</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -786,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115750616</v>
+        <v>115750658</v>
       </c>
       <c r="B3" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,26 +787,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>856542</v>
+        <v>856450</v>
       </c>
       <c r="R3" t="n">
-        <v>7476203</v>
+        <v>7476261</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -867,13 +853,17 @@
           <t>2024-04-06</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -889,108 +879,6 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>116387200</v>
-      </c>
-      <c r="B4" t="n">
-        <v>56490</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>100138</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Tetrao urogallus</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Kuusinvaaranoja, Nb</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>856561</v>
-      </c>
-      <c r="R4" t="n">
-        <v>7476268</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Pajala</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Pajala</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2024-04-22</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2024-04-22</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Marie Karlsson</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Marie Karlsson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36241-2023 artfynd.xlsx
+++ b/artfynd/A 36241-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115750616</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,8 +889,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115750658</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>